--- a/data/trans_dic/IP19C03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por empastes</t>
+          <t>Menores que en su última visita al dentista fue por empastes (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,54; 35,67</t>
+          <t>16,08; 35,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,76; 36,82</t>
+          <t>15,5; 36,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,48; 47,33</t>
+          <t>15,23; 45,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,62; 50,03</t>
+          <t>8,46; 51,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,15; 33,11</t>
+          <t>12,81; 33,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,34; 47,04</t>
+          <t>23,61; 48,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,08; 51,52</t>
+          <t>23,81; 53,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 33,95</t>
+          <t>3,96; 33,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,2; 31,37</t>
+          <t>17,1; 32,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,71; 37,7</t>
+          <t>22,36; 38,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,02; 44,31</t>
+          <t>21,49; 43,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 37,53</t>
+          <t>10,2; 36,99</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,55; 28,23</t>
+          <t>19,43; 28,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,87; 26,85</t>
+          <t>17,82; 26,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 23,41</t>
+          <t>15,26; 23,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,29; 22,11</t>
+          <t>13,85; 21,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 20,91</t>
+          <t>13,5; 21,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,93; 25,46</t>
+          <t>16,34; 24,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,37; 22,65</t>
+          <t>14,57; 22,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 22,74</t>
+          <t>14,2; 22,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,11; 23,04</t>
+          <t>17,42; 23,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,56; 24,69</t>
+          <t>18,33; 24,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,01; 21,74</t>
+          <t>16,04; 21,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,82; 20,76</t>
+          <t>15,25; 21,0</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 16,75</t>
+          <t>5,28; 16,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,3; 22,28</t>
+          <t>8,8; 22,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 14,02</t>
+          <t>3,84; 13,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,6; 22,03</t>
+          <t>10,47; 22,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,45; 24,69</t>
+          <t>10,03; 24,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 13,51</t>
+          <t>3,69; 13,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 18,2</t>
+          <t>7,13; 18,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 18,28</t>
+          <t>7,3; 19,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 17,81</t>
+          <t>8,86; 17,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,62; 15,68</t>
+          <t>7,73; 16,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 14,22</t>
+          <t>6,25; 13,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 18,29</t>
+          <t>9,71; 17,83</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,27; 24,45</t>
+          <t>17,59; 24,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,58; 24,13</t>
+          <t>17,28; 24,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 20,23</t>
+          <t>13,99; 20,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,61; 21,23</t>
+          <t>14,41; 21,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,55; 20,63</t>
+          <t>14,43; 21,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,99; 22,91</t>
+          <t>15,88; 22,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,31; 21,83</t>
+          <t>14,87; 21,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,19; 19,8</t>
+          <t>13,49; 19,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,81; 21,81</t>
+          <t>16,96; 21,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 22,31</t>
+          <t>17,62; 22,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,38; 19,96</t>
+          <t>15,58; 20,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 19,27</t>
+          <t>14,4; 19,4</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por empastes (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>11593</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11734</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6269</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7165</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9430</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15014</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10399</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3885</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>21023</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>26748</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16668</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>11050</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>7546; 16707</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7336; 17395</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3371; 10050</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2515; 15375</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5495; 14376</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10280; 20984</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6700; 14982</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1009; 8630</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>15359; 29090</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>20320; 34832</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10806; 21832</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5631; 20424</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>53953</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48627</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48382</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>46329</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>41781</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49828</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>46491</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>58420</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>95734</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>98455</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>94872</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>104749</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>44363; 65344</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39279; 58022</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38580; 59721</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36255; 57290</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>33173; 51985</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>39363; 60050</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>36862; 57449</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>45884; 73834</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>82571; 112001</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>84551; 113335</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>81088; 108838</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>89214; 122792</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12583</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6980</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15412</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>12260</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6277</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>16483</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>19503</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18860</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17181</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>31895</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4000; 12231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7530; 19005</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3369; 11649</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10478; 22164</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7335; 17999</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3033; 10942</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6256; 16223</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>9931; 26271</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>13185; 26582</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12969; 26852</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10963; 23975</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>22929; 42087</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>72789</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72944</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>61631</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>68906</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>63471</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67090</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>78788</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>136260</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>144064</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>128721</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>147694</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>61716; 87218</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>61062; 85384</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>50723; 73943</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>56430; 84026</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>52195; 76163</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>58221; 83474</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>54839; 79158</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>65330; 96364</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>120886; 152067</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>126829; 162877</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>113958; 147795</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>126168; 169935</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,08; 35,6</t>
+          <t>15,13; 36,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,5; 36,75</t>
+          <t>15,61; 35,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,23; 45,39</t>
+          <t>15,23; 45,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,46; 51,71</t>
+          <t>9,21; 50,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,81; 33,52</t>
+          <t>12,49; 32,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,61; 48,2</t>
+          <t>22,38; 47,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,81; 53,24</t>
+          <t>22,54; 53,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,96; 33,86</t>
+          <t>3,88; 31,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,1; 32,39</t>
+          <t>16,99; 31,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,36; 38,34</t>
+          <t>22,03; 38,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,49; 43,42</t>
+          <t>22,91; 45,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,2; 36,99</t>
+          <t>9,74; 36,69</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,43; 28,62</t>
+          <t>19,28; 28,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,82; 26,32</t>
+          <t>17,88; 26,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,26; 23,63</t>
+          <t>15,11; 23,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,85; 21,88</t>
+          <t>13,68; 21,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,5; 21,16</t>
+          <t>13,16; 20,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,34; 24,93</t>
+          <t>16,48; 25,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,57; 22,71</t>
+          <t>14,27; 22,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,2; 22,86</t>
+          <t>13,98; 22,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,42; 23,63</t>
+          <t>17,47; 23,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,33; 24,56</t>
+          <t>18,47; 24,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,04; 21,52</t>
+          <t>16,13; 22,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,25; 21,0</t>
+          <t>15,12; 21,06</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 16,16</t>
+          <t>4,95; 15,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,8; 22,22</t>
+          <t>8,84; 22,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 13,28</t>
+          <t>4,1; 13,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,47; 22,15</t>
+          <t>10,52; 22,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 24,62</t>
+          <t>10,33; 24,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 13,32</t>
+          <t>3,52; 13,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 18,5</t>
+          <t>7,32; 18,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 19,32</t>
+          <t>7,34; 18,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 17,86</t>
+          <t>8,89; 17,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 16,01</t>
+          <t>7,6; 15,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 13,67</t>
+          <t>6,12; 13,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 17,83</t>
+          <t>9,7; 17,75</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,59; 24,85</t>
+          <t>17,8; 24,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,28; 24,16</t>
+          <t>17,13; 24,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,99; 20,39</t>
+          <t>14,16; 20,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,41; 21,46</t>
+          <t>14,03; 21,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 21,06</t>
+          <t>14,62; 20,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,88; 22,77</t>
+          <t>16,33; 22,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,87; 21,47</t>
+          <t>15,14; 21,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,49; 19,89</t>
+          <t>13,07; 19,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 21,34</t>
+          <t>16,79; 21,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,62; 22,62</t>
+          <t>17,47; 22,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,58; 20,21</t>
+          <t>15,39; 19,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,4; 19,4</t>
+          <t>14,79; 19,38</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7546; 16707</t>
+          <t>7100; 16923</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7336; 17395</t>
+          <t>7387; 16774</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3371; 10050</t>
+          <t>3372; 10161</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2515; 15375</t>
+          <t>2738; 14937</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5495; 14376</t>
+          <t>5356; 14055</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10280; 20984</t>
+          <t>9745; 20465</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6700; 14982</t>
+          <t>6344; 15192</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1009; 8630</t>
+          <t>988; 8149</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15359; 29090</t>
+          <t>15260; 28185</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20320; 34832</t>
+          <t>20017; 34662</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10806; 21832</t>
+          <t>11518; 22840</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5631; 20424</t>
+          <t>5378; 20259</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44363; 65344</t>
+          <t>44029; 64475</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39279; 58022</t>
+          <t>39428; 59292</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38580; 59721</t>
+          <t>38192; 58583</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36255; 57290</t>
+          <t>35819; 57175</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33173; 51985</t>
+          <t>32326; 50857</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39363; 60050</t>
+          <t>39706; 60478</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36862; 57449</t>
+          <t>36090; 57092</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45884; 73834</t>
+          <t>45170; 73881</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82571; 112001</t>
+          <t>82825; 109755</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84551; 113335</t>
+          <t>85208; 113070</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81088; 108838</t>
+          <t>81571; 111389</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>89214; 122792</t>
+          <t>88421; 123167</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4000; 12231</t>
+          <t>3750; 12064</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7530; 19005</t>
+          <t>7566; 19154</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3369; 11649</t>
+          <t>3596; 11996</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10478; 22164</t>
+          <t>10532; 22080</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7335; 17999</t>
+          <t>7551; 17714</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3033; 10942</t>
+          <t>2891; 11382</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6256; 16223</t>
+          <t>6424; 15964</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9931; 26271</t>
+          <t>9980; 25530</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13185; 26582</t>
+          <t>13233; 26480</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12969; 26852</t>
+          <t>12746; 26025</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10963; 23975</t>
+          <t>10734; 24126</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22929; 42087</t>
+          <t>22883; 41900</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61716; 87218</t>
+          <t>62455; 85858</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61062; 85384</t>
+          <t>60546; 84849</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50723; 73943</t>
+          <t>51337; 73260</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56430; 84026</t>
+          <t>54937; 82922</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52195; 76163</t>
+          <t>52878; 75264</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58221; 83474</t>
+          <t>59864; 83812</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54839; 79158</t>
+          <t>55840; 81047</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65330; 96364</t>
+          <t>63316; 94934</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120886; 152067</t>
+          <t>119633; 152819</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>126829; 162877</t>
+          <t>125795; 161024</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>113958; 147795</t>
+          <t>112577; 145356</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>126168; 169935</t>
+          <t>129528; 169743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C03-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21,99%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34,49%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36,95%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>24,7%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>24,79%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>28,32%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24,1%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,95%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,13; 36,06</t>
+          <t>13,15; 33,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,61; 35,44</t>
+          <t>22,34; 47,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,23; 45,89</t>
+          <t>22,08; 51,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,21; 50,24</t>
+          <t>4,1; 35,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 32,77</t>
+          <t>15,54; 35,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,38; 47,01</t>
+          <t>15,76; 36,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,54; 53,99</t>
+          <t>14,48; 47,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 31,98</t>
+          <t>7,43; 31,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,99; 31,38</t>
+          <t>17,2; 31,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,03; 38,15</t>
+          <t>21,71; 37,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22,91; 45,42</t>
+          <t>23,02; 44,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 36,69</t>
+          <t>8,37; 27,63</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20,68%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>23,63%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>22,06%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>19,14%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,28; 28,24</t>
+          <t>13,53; 20,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,88; 26,89</t>
+          <t>16,93; 25,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,11; 23,18</t>
+          <t>14,37; 22,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,68; 21,84</t>
+          <t>14,15; 22,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,16; 20,7</t>
+          <t>19,55; 28,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,48; 25,1</t>
+          <t>17,87; 26,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,27; 22,57</t>
+          <t>15,14; 23,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,98; 22,87</t>
+          <t>14,28; 22,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,47; 23,15</t>
+          <t>17,11; 23,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,47; 24,51</t>
+          <t>18,56; 24,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,13; 22,03</t>
+          <t>16,01; 21,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,12; 21,06</t>
+          <t>14,86; 20,75</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16,77%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10,98%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,57%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14,71%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>7,96%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16,77%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 15,94</t>
+          <t>10,45; 24,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,84; 22,39</t>
+          <t>3,95; 13,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 13,67</t>
+          <t>6,6; 18,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,52; 22,06</t>
+          <t>6,5; 16,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,33; 24,23</t>
+          <t>5,11; 16,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 13,86</t>
+          <t>9,3; 22,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 18,2</t>
+          <t>4,26; 14,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 18,78</t>
+          <t>9,29; 21,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,89; 17,8</t>
+          <t>8,9; 17,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 15,52</t>
+          <t>7,62; 15,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 13,75</t>
+          <t>6,42; 14,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 17,75</t>
+          <t>9,29; 17,17</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>20,74%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20,64%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 24,47</t>
+          <t>14,55; 20,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,13; 24,01</t>
+          <t>15,99; 22,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,16; 20,2</t>
+          <t>15,31; 21,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,03; 21,17</t>
+          <t>12,59; 19,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,62; 20,81</t>
+          <t>17,27; 24,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 22,86</t>
+          <t>17,58; 24,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,14; 21,98</t>
+          <t>13,77; 20,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 19,6</t>
+          <t>14,04; 20,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,79; 21,44</t>
+          <t>16,81; 21,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,47; 22,37</t>
+          <t>17,74; 22,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,39; 19,87</t>
+          <t>15,38; 19,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,79; 19,38</t>
+          <t>14,34; 18,67</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9430</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15014</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10399</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3916</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>11593</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>11734</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6269</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7165</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9430</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15014</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10399</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>8390</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7100; 16923</t>
+          <t>5640; 14203</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7387; 16774</t>
+          <t>9725; 20481</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3372; 10161</t>
+          <t>6214; 14497</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2738; 14937</t>
+          <t>995; 8638</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5356; 14055</t>
+          <t>7293; 16738</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9745; 20465</t>
+          <t>7458; 17427</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6344; 15192</t>
+          <t>3205; 10478</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>988; 8149</t>
+          <t>1978; 8326</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15260; 28185</t>
+          <t>15446; 28176</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20017; 34662</t>
+          <t>19730; 34250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11518; 22840</t>
+          <t>11576; 22279</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5378; 20259</t>
+          <t>4262; 14073</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41781</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49828</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46491</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>54979</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>53953</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>48627</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>48382</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>46329</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41781</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49828</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>46491</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>58420</t>
+          <t>47378</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>104749</t>
+          <t>102356</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44029; 64475</t>
+          <t>33256; 51383</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39428; 59292</t>
+          <t>40789; 61343</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38192; 58583</t>
+          <t>36340; 57282</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35819; 57175</t>
+          <t>43801; 70058</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32326; 50857</t>
+          <t>44639; 64446</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39706; 60478</t>
+          <t>39402; 59205</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36090; 57092</t>
+          <t>38252; 59163</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45170; 73881</t>
+          <t>37999; 58620</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82825; 109755</t>
+          <t>81130; 109198</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85208; 113070</t>
+          <t>85611; 113919</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81571; 111389</t>
+          <t>80951; 109922</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88421; 123167</t>
+          <t>85546; 119452</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12260</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6277</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13976</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>7243</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>12583</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>6980</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15412</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12260</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6277</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10201</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16483</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31895</t>
+          <t>29436</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3750; 12064</t>
+          <t>7644; 18051</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7566; 19154</t>
+          <t>3245; 11092</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3596; 11996</t>
+          <t>5790; 15957</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10532; 22080</t>
+          <t>8267; 21390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7551; 17714</t>
+          <t>3871; 12679</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2891; 11382</t>
+          <t>7952; 19057</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6424; 15964</t>
+          <t>3734; 12304</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9980; 25530</t>
+          <t>9622; 22302</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13233; 26480</t>
+          <t>13237; 26507</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12746; 26025</t>
+          <t>12782; 26287</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10734; 24126</t>
+          <t>11264; 24943</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22883; 41900</t>
+          <t>21454; 39625</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>97</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63471</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67090</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72870</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>72789</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>72944</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>61631</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>68906</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>63471</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>71120</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67090</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>78788</t>
+          <t>67312</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>147694</t>
+          <t>140182</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62455; 85858</t>
+          <t>52631; 74619</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60546; 84849</t>
+          <t>58627; 83973</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51337; 73260</t>
+          <t>56471; 80516</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54937; 82922</t>
+          <t>58072; 88226</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52878; 75264</t>
+          <t>60600; 85800</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59864; 83812</t>
+          <t>62117; 85259</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55840; 81047</t>
+          <t>49923; 73348</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63316; 94934</t>
+          <t>55645; 79711</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>119633; 152819</t>
+          <t>119807; 155465</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>125795; 161024</t>
+          <t>127695; 160607</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>112577; 145356</t>
+          <t>112503; 146019</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>129528; 169743</t>
+          <t>122944; 160070</t>
         </is>
       </c>
     </row>
